--- a/data/football/exports/backtesting/prediction_snapshot_archive.xlsx
+++ b/data/football/exports/backtesting/prediction_snapshot_archive.xlsx
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD6" t="n">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD7" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD8" t="n">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC8" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD9" t="n">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD10" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="DB10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC10" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD11" t="n">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="DB11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC11" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD12" t="n">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="DB12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC12" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:30</t>
+          <t>2026-05-30 14:28:36</t>
         </is>
       </c>
       <c r="AD13" t="n">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="DB13" t="inlineStr">
         <is>
-          <t>2026-05-30 10:49:32</t>
+          <t>2026-05-30 14:28:37</t>
         </is>
       </c>
       <c r="DC13" t="inlineStr">

--- a/data/football/exports/backtesting/prediction_snapshot_archive.xlsx
+++ b/data/football/exports/backtesting/prediction_snapshot_archive.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD13"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SP2_2026-05-30_Ceuta_Albacete</t>
+          <t>SP2_2026-05-31_Santander_Cadiz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -989,16 +989,16 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-30 15:15:00</t>
+          <t>2026-05-31 17:30:00</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -1006,58 +1006,58 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>7.9</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -1071,181 +1071,181 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0.2</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AG2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.6</v>
+        <v>15.8</v>
       </c>
       <c r="AK2" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="AN2" t="n">
         <v>0.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
         <v>0.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AS2" t="n">
         <v>1.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA2" t="n">
         <v>0.8</v>
       </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>1.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG2" t="n">
         <v>0.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="BI2" t="n">
         <v>0.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
         <v>0.4</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BM2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BO2" t="n">
         <v>4.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.312</v>
+        <v>0.646</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.266</v>
+        <v>0.232</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.422</v>
+        <v>0.123</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>Away Win</t>
+          <t>Home Win</t>
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.422</v>
+        <v>0.646</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.72</v>
+        <v>0.88</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.834</v>
+        <v>0.882</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.637</v>
+        <v>0.677</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.415</v>
+        <v>0.445</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.717</v>
+        <v>0.752</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.48</v>
+        <v>5.92</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.32</v>
+        <v>3.32</v>
       </c>
       <c r="CD2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.782</v>
+        <v>0.746</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.676</v>
+        <v>0.644</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.58</v>
+        <v>0.549</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>0.834</v>
+        <v>0.882</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -1261,14 +1261,14 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="CM2" t="n">
         <v>1</v>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
@@ -1282,11 +1282,11 @@
         </is>
       </c>
       <c r="CQ2" t="n">
-        <v>0.706</v>
+        <v>0.794</v>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU2" t="n">
         <v>1</v>
@@ -1304,29 +1304,29 @@
         <v>1</v>
       </c>
       <c r="CW2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CX2" t="n">
         <v>1</v>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
+          <t>Result: Home Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>SP2_2026-05-30_ceuta_albacete_away win</t>
+          <t>SP2_2026-05-31_santander_cadiz_home win</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SP2_2026-05-30_Granada_Sp Gijon</t>
+          <t>SP2_2026-05-31_Cordoba_Huesca</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-30 20:00:00</t>
+          <t>2026-05-31 20:00:00</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -1384,58 +1384,58 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Sp Gijon</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="P3" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.76</v>
+        <v>4.74</v>
       </c>
       <c r="R3" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.95</v>
+        <v>5.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -1449,181 +1449,181 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AN3" t="n">
         <v>0.8</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AO3" t="n">
         <v>0.8</v>
       </c>
-      <c r="AI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AP3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX3" t="n">
         <v>0.2</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="AY3" t="n">
         <v>0.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB3" t="n">
         <v>1.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="BI3" t="n">
         <v>0.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="BL3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.336</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.25</v>
+        <v>0.232</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.414</v>
+        <v>0.207</v>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>Away Win</t>
+          <t>Home Win</t>
         </is>
       </c>
       <c r="BT3" t="n">
-        <v>0.414</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.12</v>
+        <v>1.72</v>
       </c>
       <c r="BV3" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.874</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.67</v>
+        <v>0.617</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.36</v>
+        <v>6.68</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.36</v>
+        <v>5.12</v>
       </c>
       <c r="CD3" t="n">
-        <v>8.720000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.823</v>
+        <v>1</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.713</v>
+        <v>0.911</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.613</v>
+        <v>0.794</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.521</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="CJ3" t="n">
-        <v>0.874</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
@@ -1639,14 +1639,14 @@
         </is>
       </c>
       <c r="CL3" t="n">
-        <v>0.823</v>
+        <v>1</v>
       </c>
       <c r="CM3" t="n">
         <v>1</v>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
@@ -1660,11 +1660,11 @@
         </is>
       </c>
       <c r="CQ3" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
@@ -1689,22 +1689,22 @@
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
+          <t>Result: Home Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>SP2_2026-05-30_granada_sp gijon_away win</t>
+          <t>SP2_2026-05-31_cordoba_huesca_home win</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SP2_2026-05-30_Sociedad B_Cultural Leonesa</t>
+          <t>SP2_2026-05-31_Zaragoza_Malaga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1745,16 +1745,16 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-30 15:15:00</t>
+          <t>2026-05-31 17:30:00</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -1762,160 +1762,160 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Cultural Leonesa</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="O4" t="n">
-        <v>2.25</v>
+        <v>4.34</v>
       </c>
       <c r="P4" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.91</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>football-data.co.uk fixtures.csv</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>https://www.football-data.co.uk/fixtures.csv</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-05-31 11:30:51</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.8</v>
       </c>
-      <c r="V4" t="n">
-        <v>2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:36</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AJ4" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AN4" t="n">
         <v>0.4</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AO4" t="n">
         <v>0.4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.6</v>
       </c>
       <c r="AP4" t="n">
         <v>0.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX4" t="n">
         <v>0.6</v>
       </c>
-      <c r="AT4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AY4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.4</v>
+        <v>15.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="BG4" t="n">
         <v>1</v>
@@ -1927,81 +1927,81 @@
         <v>0.2</v>
       </c>
       <c r="BJ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM4" t="n">
         <v>1.4</v>
       </c>
-      <c r="BK4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BN4" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.37</v>
+        <v>0.262</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.311</v>
+        <v>0.229</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.319</v>
+        <v>0.509</v>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>Home Win</t>
+          <t>Away Win</t>
         </is>
       </c>
       <c r="BT4" t="n">
-        <v>0.37</v>
+        <v>0.509</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.72</v>
+        <v>3.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.794</v>
+        <v>0.962</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.603</v>
+        <v>0.743</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.39</v>
+        <v>0.495</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.73</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.04</v>
+        <v>4.96</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.24</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.789</v>
+        <v>0.823</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.713</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.585</v>
+        <v>0.613</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.495</v>
+        <v>0.521</v>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="CJ4" t="n">
-        <v>0.794</v>
+        <v>0.962</v>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
@@ -2017,14 +2017,14 @@
         </is>
       </c>
       <c r="CL4" t="n">
-        <v>0.789</v>
+        <v>0.823</v>
       </c>
       <c r="CM4" t="n">
         <v>1</v>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
@@ -2038,16 +2038,16 @@
         </is>
       </c>
       <c r="CQ4" t="n">
-        <v>0.644</v>
+        <v>0.769</v>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>C Tier</t>
+          <t>B Tier</t>
         </is>
       </c>
       <c r="CT4" t="n">
@@ -2063,26 +2063,26 @@
         <v>2</v>
       </c>
       <c r="CX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>Result: Home Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
+          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
@@ -2092,14 +2092,14 @@
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>SP2_2026-05-30_sociedad b_cultural leonesa_home win</t>
+          <t>SP2_2026-05-31_zaragoza_malaga_away win</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_Santander_Cadiz</t>
+          <t>SP2_2026-05-31_Almeria_Valladolid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2140,40 +2140,40 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.9</v>
+        <v>6.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="T5" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="U5" t="n">
         <v>1.53</v>
@@ -2182,13 +2182,13 @@
         <v>2.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
         <v>2.45</v>
@@ -2205,38 +2205,38 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15.8</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="AN5" t="n">
         <v>0.8</v>
@@ -2245,7 +2245,7 @@
         <v>0.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.4</v>
@@ -2254,192 +2254,192 @@
         <v>0.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AW5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AX5" t="n">
         <v>0.4</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1.8</v>
       </c>
-      <c r="BC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BJ5" t="n">
+      <c r="BP5" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>Home Win</t>
+        </is>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>Over 1.5 Goals</t>
+        </is>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>Over 7.5 Corners</t>
+        </is>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>B Tier</t>
+        </is>
+      </c>
+      <c r="CT5" t="n">
         <v>0</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="CU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW5" t="n">
         <v>2</v>
       </c>
-      <c r="BN5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>Home Win</t>
-        </is>
-      </c>
-      <c r="BT5" t="n">
-        <v>0.646</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>Over 1.5 Goals</t>
-        </is>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>Over 7.5 Corners</t>
-        </is>
-      </c>
-      <c r="CL5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="CQ5" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>B Tier</t>
-        </is>
-      </c>
-      <c r="CT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>3</v>
-      </c>
       <c r="CX5" t="n">
         <v>1</v>
       </c>
@@ -2450,17 +2450,17 @@
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
@@ -2470,14 +2470,14 @@
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_santander_cadiz_home win</t>
+          <t>SP2_2026-05-31_almeria_valladolid_home win</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_Cordoba_Huesca</t>
+          <t>SP2_2026-05-31_Castellon_Eibar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-31 20:00:00</t>
+          <t>2026-05-31 17:30:00</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -2518,58 +2518,58 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>3.35</v>
+        <v>4.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.74</v>
+        <v>5.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
         <v>5.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -2583,17 +2583,17 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AG6" t="n">
         <v>0.2</v>
@@ -2602,112 +2602,112 @@
         <v>1.8</v>
       </c>
       <c r="AI6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1.2</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="AR6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
         <v>5.8</v>
       </c>
-      <c r="AL6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AQ6" t="n">
+      <c r="AV6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AX6" t="n">
         <v>0.6</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.4</v>
       </c>
-      <c r="AT6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BC6" t="n">
-        <v>11.2</v>
+        <v>11.8</v>
       </c>
       <c r="BD6" t="n">
         <v>3.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
         <v>0.6</v>
       </c>
       <c r="BH6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK6" t="n">
         <v>0.6</v>
       </c>
-      <c r="BI6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.2</v>
-      </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BO6" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.409</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.232</v>
+        <v>0.293</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.207</v>
+        <v>0.298</v>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
@@ -2715,49 +2715,49 @@
         </is>
       </c>
       <c r="BT6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.409</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="BV6" t="n">
-        <v>1.08</v>
+        <v>1.64</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="BX6" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CA6" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="BY6" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.7</v>
-      </c>
       <c r="CB6" t="n">
-        <v>6.68</v>
+        <v>6.48</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.12</v>
+        <v>3</v>
       </c>
       <c r="CD6" t="n">
-        <v>11.8</v>
+        <v>9.48</v>
       </c>
       <c r="CE6" t="n">
-        <v>1</v>
+        <v>0.877</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.911</v>
+        <v>0.762</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.794</v>
+        <v>0.658</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="CJ6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.906</v>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
@@ -2773,14 +2773,14 @@
         </is>
       </c>
       <c r="CL6" t="n">
-        <v>1</v>
+        <v>0.877</v>
       </c>
       <c r="CM6" t="n">
         <v>1</v>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
@@ -2794,11 +2794,11 @@
         </is>
       </c>
       <c r="CQ6" t="n">
-        <v>0.77</v>
+        <v>0.725</v>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>High</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -2828,17 +2828,17 @@
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC6" t="inlineStr">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="DD6" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_cordoba_huesca_home win</t>
+          <t>SP2_2026-05-31_castellon_eibar_home win</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_Zaragoza_Malaga</t>
+          <t>SP2_2026-05-31_La Coruna_Las Palmas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2896,58 +2896,58 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Zaragoza</t>
+          <t>La Coruna</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4.34</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.98</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.95</v>
-      </c>
       <c r="X7" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -2961,181 +2961,181 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.8</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO7" t="n">
         <v>0.6</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AP7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AN7" t="n">
+      <c r="AR7" t="n">
         <v>0.4</v>
       </c>
-      <c r="AO7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
       <c r="AS7" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>15.8</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
         <v>4.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BM7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>Home Win</t>
+        </is>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BV7" t="n">
         <v>1.4</v>
       </c>
-      <c r="BN7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>Away Win</t>
-        </is>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BW7" t="n">
-        <v>3.56</v>
+        <v>3.12</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.962</v>
+        <v>0.874</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.743</v>
+        <v>0.67</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.495</v>
+        <v>0.44</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="CB7" t="n">
         <v>4.96</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.76</v>
+        <v>4.08</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.720000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.823</v>
+        <v>0.846</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.713</v>
+        <v>0.733</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.613</v>
+        <v>0.632</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.521</v>
+        <v>0.539</v>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="CJ7" t="n">
-        <v>0.962</v>
+        <v>0.874</v>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
@@ -3151,14 +3151,14 @@
         </is>
       </c>
       <c r="CL7" t="n">
-        <v>0.823</v>
+        <v>0.846</v>
       </c>
       <c r="CM7" t="n">
         <v>1</v>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
@@ -3172,11 +3172,11 @@
         </is>
       </c>
       <c r="CQ7" t="n">
-        <v>0.769</v>
+        <v>0.7</v>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>High</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
+          <t>Result: Home Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC7" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="DD7" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_zaragoza_malaga_away win</t>
+          <t>SP2_2026-05-31_la coruna_las palmas_home win</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_Almeria_Valladolid</t>
+          <t>SP2_2026-05-31_Leganes_Mirandes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-31 17:30:00</t>
+          <t>2026-05-31 20:00:00</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -3274,58 +3274,58 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.54</v>
+        <v>3.29</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="S8" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="X8" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -3339,181 +3339,181 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0.2</v>
       </c>
       <c r="AG8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN8" t="n">
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>0.8</v>
       </c>
-      <c r="AO8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AU8" t="n">
         <v>3.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="BB8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL8" t="n">
         <v>1.4</v>
       </c>
-      <c r="BC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL8" t="n">
+      <c r="BM8" t="n">
         <v>1.2</v>
       </c>
-      <c r="BM8" t="n">
-        <v>0.2</v>
-      </c>
       <c r="BN8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.512</v>
+        <v>0.333</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.242</v>
+        <v>0.271</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.246</v>
+        <v>0.396</v>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>Home Win</t>
+          <t>Away Win</t>
         </is>
       </c>
       <c r="BT8" t="n">
-        <v>0.512</v>
+        <v>0.396</v>
       </c>
       <c r="BU8" t="n">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="BV8" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.24</v>
+        <v>2.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.898</v>
+        <v>0.802</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.455</v>
+        <v>0.395</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.725</v>
+        <v>0.66</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
       <c r="CC8" t="n">
-        <v>5.04</v>
+        <v>5.32</v>
       </c>
       <c r="CD8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.857</v>
+        <v>0.883</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.744</v>
+        <v>0.767</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.641</v>
+        <v>0.662</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.547</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="CJ8" t="n">
-        <v>0.898</v>
+        <v>0.802</v>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
@@ -3529,14 +3529,14 @@
         </is>
       </c>
       <c r="CL8" t="n">
-        <v>0.857</v>
+        <v>0.883</v>
       </c>
       <c r="CM8" t="n">
         <v>1</v>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
@@ -3550,16 +3550,16 @@
         </is>
       </c>
       <c r="CQ8" t="n">
-        <v>0.753</v>
+        <v>0.68</v>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>High</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="CT8" t="n">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>Result: Home Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
+          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC8" t="inlineStr">
@@ -3604,14 +3604,14 @@
       </c>
       <c r="DD8" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_almeria_valladolid_home win</t>
+          <t>SP2_2026-05-31_leganes_mirandes_away win</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_Castellon_Eibar</t>
+          <t>SP2_2026-05-31_Burgos_Andorra</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3652,58 +3652,58 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Castellon</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P9" t="n">
-        <v>4.17</v>
+        <v>3.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.08</v>
+        <v>5.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>5.5</v>
+        <v>6.33</v>
       </c>
       <c r="U9" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="X9" t="n">
-        <v>2.33</v>
+        <v>1.82</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -3717,65 +3717,65 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AG9" t="n">
         <v>0.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.6</v>
+        <v>10.8</v>
       </c>
       <c r="AK9" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="AP9" t="n">
         <v>0.4</v>
       </c>
       <c r="AQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AS9" t="n">
         <v>1.2</v>
       </c>
-      <c r="AR9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW9" t="n">
         <v>1.8</v>
@@ -3790,28 +3790,28 @@
         <v>0.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.8</v>
+        <v>16.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="BG9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BH9" t="n">
         <v>0.6</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0.8</v>
       </c>
       <c r="BI9" t="n">
         <v>0.4</v>
@@ -3823,75 +3823,75 @@
         <v>0.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.409</v>
+        <v>0.312</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.293</v>
+        <v>0.266</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.298</v>
+        <v>0.422</v>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>Home Win</t>
+          <t>Away Win</t>
         </is>
       </c>
       <c r="BT9" t="n">
-        <v>0.409</v>
+        <v>0.422</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.64</v>
+        <v>0.68</v>
       </c>
       <c r="BV9" t="n">
         <v>1.64</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.28</v>
+        <v>2.32</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.906</v>
+        <v>0.714</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.697</v>
+        <v>0.537</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="CB9" t="n">
-        <v>6.48</v>
+        <v>4.52</v>
       </c>
       <c r="CC9" t="n">
-        <v>3</v>
+        <v>4.28</v>
       </c>
       <c r="CD9" t="n">
-        <v>9.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.877</v>
+        <v>0.829</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.762</v>
+        <v>0.718</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.658</v>
+        <v>0.618</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="CJ9" t="n">
-        <v>0.906</v>
+        <v>0.714</v>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="CL9" t="n">
-        <v>0.877</v>
+        <v>0.829</v>
       </c>
       <c r="CM9" t="n">
         <v>1</v>
@@ -3919,25 +3919,25 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
       <c r="CQ9" t="n">
-        <v>0.725</v>
+        <v>0.641</v>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="CT9" t="n">
@@ -3953,26 +3953,26 @@
         <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>Result: Home Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
+          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC9" t="inlineStr">
@@ -3982,34 +3982,34 @@
       </c>
       <c r="DD9" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_castellon_eibar_home win</t>
+          <t>SP2_2026-05-31_burgos_andorra_away win</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SP2_2026-05-31_La Coruna_Las Palmas</t>
+          <t>B1_2026-05-31_Gent_Genk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SP2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>La Liga 2</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tier 2 - Europe Depth</t>
+          <t>Tier 1 - Elite Europe</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
@@ -4030,58 +4030,58 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>La Coruna</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V10" t="n">
         <v>2.1</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -4095,181 +4095,181 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:36</t>
+          <t>2026-05-31 11:30:51</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AG10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AO10" t="n">
         <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.6</v>
       </c>
       <c r="AP10" t="n">
         <v>0.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
         <v>1.2</v>
       </c>
-      <c r="AT10" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="BB10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>1.6</v>
       </c>
-      <c r="BC10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>3</v>
-      </c>
       <c r="BK10" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1.8</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BO10" t="n">
         <v>4.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.397</v>
+        <v>0.28</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.292</v>
+        <v>0.282</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.311</v>
+        <v>0.437</v>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>Home Win</t>
+          <t>Away Win</t>
         </is>
       </c>
       <c r="BT10" t="n">
-        <v>0.397</v>
+        <v>0.437</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.72</v>
+        <v>0.48</v>
       </c>
       <c r="BV10" t="n">
-        <v>1.4</v>
+        <v>0.88</v>
       </c>
       <c r="BW10" t="n">
-        <v>3.12</v>
+        <v>1.36</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.874</v>
+        <v>0.522</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.67</v>
+        <v>0.377</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.785</v>
+        <v>0.325</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.96</v>
+        <v>4.4</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.08</v>
+        <v>6.88</v>
       </c>
       <c r="CD10" t="n">
-        <v>9.039999999999999</v>
+        <v>11.28</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.846</v>
+        <v>1</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.733</v>
+        <v>0.878</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.632</v>
+        <v>0.764</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.539</v>
+        <v>0.66</v>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="CJ10" t="n">
-        <v>0.874</v>
+        <v>0.522</v>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="CL10" t="n">
-        <v>0.846</v>
+        <v>1</v>
       </c>
       <c r="CM10" t="n">
         <v>1</v>
@@ -4297,60 +4297,60 @@
       </c>
       <c r="CO10" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
       <c r="CQ10" t="n">
-        <v>0.7</v>
+        <v>0.612</v>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV10" t="n">
         <v>1</v>
       </c>
       <c r="CW10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CX10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>Result: Home Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
+          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:28:37</t>
+          <t>2026-05-31 11:30:53</t>
         </is>
       </c>
       <c r="DC10" t="inlineStr">
@@ -4359,1140 +4359,6 @@
         </is>
       </c>
       <c r="DD10" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-31_la coruna_las palmas_home win</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-31_Leganes_Mirandes</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-05-31 20:00:00</t>
-        </is>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Mirandes</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:36</t>
-        </is>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>Away Win</t>
-        </is>
-      </c>
-      <c r="BT11" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>Over 1.5 Goals</t>
-        </is>
-      </c>
-      <c r="CJ11" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>Over 7.5 Corners</t>
-        </is>
-      </c>
-      <c r="CL11" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="CQ11" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>C Tier</t>
-        </is>
-      </c>
-      <c r="CT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>1</v>
-      </c>
-      <c r="CY11" t="inlineStr">
-        <is>
-          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
-        </is>
-      </c>
-      <c r="CZ11" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:37</t>
-        </is>
-      </c>
-      <c r="DA11" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="DB11" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:37</t>
-        </is>
-      </c>
-      <c r="DC11" t="inlineStr">
-        <is>
-          <t>football_fixture_predictions</t>
-        </is>
-      </c>
-      <c r="DD11" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-31_leganes_mirandes_away win</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-31_Burgos_Andorra</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SP2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-05-31 17:30:00</t>
-        </is>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Burgos</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Andorra</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:36</t>
-        </is>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>Away Win</t>
-        </is>
-      </c>
-      <c r="BT12" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="CI12" t="inlineStr">
-        <is>
-          <t>Over 1.5 Goals</t>
-        </is>
-      </c>
-      <c r="CJ12" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="CK12" t="inlineStr">
-        <is>
-          <t>Over 7.5 Corners</t>
-        </is>
-      </c>
-      <c r="CL12" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN12" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="CP12" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="CQ12" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>C Tier</t>
-        </is>
-      </c>
-      <c r="CT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY12" t="inlineStr">
-        <is>
-          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
-        </is>
-      </c>
-      <c r="CZ12" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:37</t>
-        </is>
-      </c>
-      <c r="DA12" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="DB12" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:37</t>
-        </is>
-      </c>
-      <c r="DC12" t="inlineStr">
-        <is>
-          <t>football_fixture_predictions</t>
-        </is>
-      </c>
-      <c r="DD12" t="inlineStr">
-        <is>
-          <t>SP2_2026-05-31_burgos_andorra_away win</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B1_2026-05-31_Gent_Genk</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Belgian Pro League</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-05-31 17:30:00</t>
-        </is>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Genk</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>football-data.co.uk fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>https://www.football-data.co.uk/fixtures.csv</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:36</t>
-        </is>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>Away Win</t>
-        </is>
-      </c>
-      <c r="BT13" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF13" t="n">
-        <v>0.878</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="CI13" t="inlineStr">
-        <is>
-          <t>Over 1.5 Goals</t>
-        </is>
-      </c>
-      <c r="CJ13" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="CK13" t="inlineStr">
-        <is>
-          <t>Over 7.5 Corners</t>
-        </is>
-      </c>
-      <c r="CL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN13" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="CO13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="CP13" t="inlineStr">
-        <is>
-          <t>Elite</t>
-        </is>
-      </c>
-      <c r="CQ13" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="CS13" t="inlineStr">
-        <is>
-          <t>C Tier</t>
-        </is>
-      </c>
-      <c r="CT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY13" t="inlineStr">
-        <is>
-          <t>Result: Away Win | Goals: Over 1.5 Goals | Corners: Over 7.5 Corners</t>
-        </is>
-      </c>
-      <c r="CZ13" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:37</t>
-        </is>
-      </c>
-      <c r="DA13" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="DB13" t="inlineStr">
-        <is>
-          <t>2026-05-30 14:28:37</t>
-        </is>
-      </c>
-      <c r="DC13" t="inlineStr">
-        <is>
-          <t>football_fixture_predictions</t>
-        </is>
-      </c>
-      <c r="DD13" t="inlineStr">
         <is>
           <t>B1_2026-05-31_gent_genk_away win</t>
         </is>
